--- a/DatosMigracion.xlsx
+++ b/DatosMigracion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\.gemini\antigravity\scratch\AOMNIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E51BAB5-708B-44B2-B83C-C083858AC61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC85108-B471-4126-A1C4-622B43805CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FF17F83E-52DA-44F8-975A-DC2510BDF13B}"/>
+    <workbookView xWindow="6585" yWindow="4785" windowWidth="28800" windowHeight="15345" xr2:uid="{FF17F83E-52DA-44F8-975A-DC2510BDF13B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3888" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4096" uniqueCount="960">
   <si>
     <t>INGRESO</t>
   </si>
@@ -2462,9 +2462,6 @@
     <t>AH113XY</t>
   </si>
   <si>
-    <t>FIAT CRONOS 1.8 PRECISION AUT</t>
-  </si>
-  <si>
     <t>AC515DN</t>
   </si>
   <si>
@@ -2534,9 +2531,6 @@
     <t>MSJ593</t>
   </si>
   <si>
-    <t>PEUGEOT 208 L/20 1.6 LIKE PACK</t>
-  </si>
-  <si>
     <t>AF610IQ</t>
   </si>
   <si>
@@ -2648,18 +2642,12 @@
     <t>PKY728</t>
   </si>
   <si>
-    <t>FORD TERRITORY 1.8T TITANIUM L/25</t>
-  </si>
-  <si>
     <t>AH914VG</t>
   </si>
   <si>
     <t>PIN417</t>
   </si>
   <si>
-    <t>PEUGEOT 208 L/23 1.6 ALLURE PACK TIPTRONIC</t>
-  </si>
-  <si>
     <t>AG800EV</t>
   </si>
   <si>
@@ -2744,9 +2732,6 @@
     <t>AE038YH</t>
   </si>
   <si>
-    <t>RENAULT DUSTER OROCH 2.0 PRIVILEGE</t>
-  </si>
-  <si>
     <t>AD221JP</t>
   </si>
   <si>
@@ -2754,6 +2739,183 @@
   </si>
   <si>
     <t>AE460BG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOYOTA COROLLA 1.8 XEI L/14   (no me paso nada) </t>
+  </si>
+  <si>
+    <t>FIAT CRONOS 1.8 PRECISION AUT  (reclamada )</t>
+  </si>
+  <si>
+    <t>PEUGEOT 208 L/20 1.6 LIKE PACK (esperando que acuerde emi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORD KA 1.5 SE (no me paso nada) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAULT SANDERO II 1.6 16V LIFE L/23  (esperando que se migre) </t>
+  </si>
+  <si>
+    <t>CHEVROLET PRISMA 1.4 LT L/17 (esperando carta de hallazgo)</t>
+  </si>
+  <si>
+    <t>FORD TERRITORY 1.8T TITANIUM L/25 (me lo paso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEUGEOT 208 L/23 1.6 ALLURE PACK TIPTRONIC (me lo paso) </t>
+  </si>
+  <si>
+    <t>PARA FACTURAR</t>
+  </si>
+  <si>
+    <t>RENAULT DUSTER OROCH 2.0 PRIVILEGE  (reclamada )</t>
+  </si>
+  <si>
+    <t>VOLKSWAGEN GOL 1.6 5 P TRENDLINE L/19 (esperando repuesta taller) - ausente</t>
+  </si>
+  <si>
+    <t>VOLKSWAGEN TAOS 1.4 250 TSI HERO</t>
+  </si>
+  <si>
+    <t>AE888BO</t>
+  </si>
+  <si>
+    <t>VOLKSWAGEN GOL 1.6 5 P TREND L/13</t>
+  </si>
+  <si>
+    <t>OFC131</t>
+  </si>
+  <si>
+    <t>AG263FY</t>
+  </si>
+  <si>
+    <t>FIAT CRONOS 1.3 PRECISION CVT L/25</t>
+  </si>
+  <si>
+    <t>AH755FV</t>
+  </si>
+  <si>
+    <t>TOYOTA YARIS 1.5 4 PTAS XLS L/20</t>
+  </si>
+  <si>
+    <t>AE505AQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLKSWAGEN VOYAGE 1.6 L/13 COMFORTLINE </t>
+  </si>
+  <si>
+    <t>MMD556</t>
+  </si>
+  <si>
+    <t>AF925BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHEVROLET SPIN 1.8 LT 5 AS MY LINK </t>
+  </si>
+  <si>
+    <t>AB648KR</t>
+  </si>
+  <si>
+    <t>CHRYSLER JEEP RENEGADE 1.8 4X2 LONGITUDE AT</t>
+  </si>
+  <si>
+    <t>AE035YS</t>
+  </si>
+  <si>
+    <t>TOYOTA COROLLA CROSS 2.0 SEG CVT</t>
+  </si>
+  <si>
+    <t>AG941XN</t>
+  </si>
+  <si>
+    <t>CHRYSLER JOURNEY 2.4 SE L/11</t>
+  </si>
+  <si>
+    <t>LFN091</t>
+  </si>
+  <si>
+    <t>FIAT UNO 1.4 5 PTAS WAY</t>
+  </si>
+  <si>
+    <t>NQH392</t>
+  </si>
+  <si>
+    <t>AC908ED</t>
+  </si>
+  <si>
+    <t>CHEVROLET ONIX 1.0T PLUS LT L/25</t>
+  </si>
+  <si>
+    <t>AH784VE</t>
+  </si>
+  <si>
+    <t>CHEVROLET CORSA 1.4 4 P GL L/09</t>
+  </si>
+  <si>
+    <t>IWW849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAULT ALASKAN 2.3 TDI CONFORT 4X2 </t>
+  </si>
+  <si>
+    <t>AF279VS</t>
+  </si>
+  <si>
+    <t>AA456TE</t>
+  </si>
+  <si>
+    <t>RENAULT FLUENCE 2.0 PRIVILEGE CVT</t>
+  </si>
+  <si>
+    <t>KRM438</t>
+  </si>
+  <si>
+    <t>MYL038</t>
+  </si>
+  <si>
+    <t>PEUGEOT EXPERT 1.6 HDI PREMIUM 6AS</t>
+  </si>
+  <si>
+    <t>AF292ZM</t>
+  </si>
+  <si>
+    <t>PEUGEOT 208 L/20 1.6 ACTIVE TIPTRONIC</t>
+  </si>
+  <si>
+    <t>AF813DQ</t>
+  </si>
+  <si>
+    <t>FORD FOCUS L/16 1.6 5 P S</t>
+  </si>
+  <si>
+    <t>AA853FK</t>
+  </si>
+  <si>
+    <t>TOYOTA ETIOS 1.5 5 PTAS XS</t>
+  </si>
+  <si>
+    <t>NOS263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCEDES BENZ C 250 AVANTGARDE AUT </t>
+  </si>
+  <si>
+    <t>PEK853</t>
+  </si>
+  <si>
+    <t>TOYOTA HILUX 3.0 D/CAB 4X4 TD SRV</t>
+  </si>
+  <si>
+    <t>IIE912</t>
+  </si>
+  <si>
+    <t>VGuisado@sancorseguros.com</t>
+  </si>
+  <si>
+    <t>MERCEDES BENZ SPRINTER 310 COMBI 3550 12+1</t>
+  </si>
+  <si>
+    <t>NMZ354</t>
   </si>
 </sst>
 </file>
@@ -3126,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F107DE2-B471-461B-9D4D-EFED0DBA37C8}">
-  <dimension ref="A1:N489"/>
+  <dimension ref="A1:N516"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -19573,10 +19735,10 @@
         <v>57</v>
       </c>
       <c r="E380" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F380" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="G380" t="s">
         <v>6</v>
@@ -19595,6 +19757,9 @@
       </c>
       <c r="L380" t="s">
         <v>21</v>
+      </c>
+      <c r="M380" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
@@ -19699,13 +19864,13 @@
         <v>65</v>
       </c>
       <c r="E383" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F383" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G383" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H383" t="s">
         <v>210</v>
@@ -19724,6 +19889,9 @@
       </c>
       <c r="M383" s="1">
         <v>46085</v>
+      </c>
+      <c r="N383" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
@@ -20532,13 +20700,13 @@
         <v>14</v>
       </c>
       <c r="E402" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F402" t="s">
         <v>23</v>
       </c>
       <c r="G402" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H402" t="s">
         <v>761</v>
@@ -20557,6 +20725,9 @@
       </c>
       <c r="M402" s="1">
         <v>46085</v>
+      </c>
+      <c r="N402" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.25">
@@ -20793,13 +20964,13 @@
         <v>214</v>
       </c>
       <c r="E408" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F408" t="s">
         <v>130</v>
       </c>
       <c r="G408" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H408" t="s">
         <v>496</v>
@@ -20815,6 +20986,12 @@
       </c>
       <c r="L408" t="s">
         <v>21</v>
+      </c>
+      <c r="M408" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N408" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.25">
@@ -21127,16 +21304,16 @@
         <v>92</v>
       </c>
       <c r="E416" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F416" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G416" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H416" t="s">
-        <v>592</v>
+        <v>901</v>
       </c>
       <c r="I416" t="s">
         <v>593</v>
@@ -21149,6 +21326,12 @@
       </c>
       <c r="L416" t="s">
         <v>21</v>
+      </c>
+      <c r="M416" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N416" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.25">
@@ -21209,13 +21392,13 @@
         <v>95</v>
       </c>
       <c r="E418" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F418" t="s">
         <v>23</v>
       </c>
       <c r="G418" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H418" t="s">
         <v>785</v>
@@ -21231,6 +21414,12 @@
       </c>
       <c r="L418" t="s">
         <v>21</v>
+      </c>
+      <c r="M418" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N418" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.25">
@@ -21335,13 +21524,13 @@
         <v>98</v>
       </c>
       <c r="E421" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F421" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G421" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H421" t="s">
         <v>790</v>
@@ -21360,6 +21549,9 @@
       </c>
       <c r="M421" s="1">
         <v>46085</v>
+      </c>
+      <c r="N421" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.25">
@@ -21376,13 +21568,13 @@
         <v>489</v>
       </c>
       <c r="E422" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F422" t="s">
         <v>23</v>
       </c>
       <c r="G422" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H422" t="s">
         <v>359</v>
@@ -21398,6 +21590,12 @@
       </c>
       <c r="L422" t="s">
         <v>21</v>
+      </c>
+      <c r="M422" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N422" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.25">
@@ -21546,13 +21744,13 @@
         <v>37</v>
       </c>
       <c r="E426" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F426" t="s">
         <v>23</v>
       </c>
       <c r="G426" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H426" t="s">
         <v>799</v>
@@ -21571,6 +21769,9 @@
       </c>
       <c r="M426" s="1">
         <v>46085</v>
+      </c>
+      <c r="N426" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.25">
@@ -21631,13 +21832,13 @@
         <v>52</v>
       </c>
       <c r="E428" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F428" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G428" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H428" t="s">
         <v>802</v>
@@ -21656,6 +21857,9 @@
       </c>
       <c r="M428" s="1">
         <v>46085</v>
+      </c>
+      <c r="N428" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.25">
@@ -21672,13 +21876,13 @@
         <v>37</v>
       </c>
       <c r="E429" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F429" t="s">
         <v>23</v>
       </c>
       <c r="G429" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H429" t="s">
         <v>804</v>
@@ -21697,6 +21901,9 @@
       </c>
       <c r="M429" s="1">
         <v>46085</v>
+      </c>
+      <c r="N429" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.25">
@@ -21713,13 +21920,13 @@
         <v>43</v>
       </c>
       <c r="E430" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F430" t="s">
         <v>23</v>
       </c>
       <c r="G430" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H430" t="s">
         <v>725</v>
@@ -21738,6 +21945,9 @@
       </c>
       <c r="M430" s="1">
         <v>46085</v>
+      </c>
+      <c r="N430" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.25">
@@ -21798,7 +22008,7 @@
         <v>92</v>
       </c>
       <c r="E432" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="F432" t="s">
         <v>23</v>
@@ -21807,10 +22017,10 @@
         <v>6</v>
       </c>
       <c r="H432" t="s">
+        <v>902</v>
+      </c>
+      <c r="I432" t="s">
         <v>808</v>
-      </c>
-      <c r="I432" t="s">
-        <v>809</v>
       </c>
       <c r="J432" t="s">
         <v>20</v>
@@ -21848,7 +22058,7 @@
         <v>326</v>
       </c>
       <c r="I433" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J433" t="s">
         <v>20</v>
@@ -21880,19 +22090,19 @@
         <v>129</v>
       </c>
       <c r="E434" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F434" t="s">
         <v>130</v>
       </c>
       <c r="G434" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H434" t="s">
+        <v>810</v>
+      </c>
+      <c r="I434" t="s">
         <v>811</v>
-      </c>
-      <c r="I434" t="s">
-        <v>812</v>
       </c>
       <c r="J434" t="s">
         <v>20</v>
@@ -21902,6 +22112,12 @@
       </c>
       <c r="L434" t="s">
         <v>21</v>
+      </c>
+      <c r="M434" s="1">
+        <v>46090</v>
+      </c>
+      <c r="N434" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.25">
@@ -21918,19 +22134,19 @@
         <v>57</v>
       </c>
       <c r="E435" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F435" t="s">
         <v>23</v>
       </c>
       <c r="G435" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H435" t="s">
+        <v>812</v>
+      </c>
+      <c r="I435" t="s">
         <v>813</v>
-      </c>
-      <c r="I435" t="s">
-        <v>814</v>
       </c>
       <c r="J435" t="s">
         <v>20</v>
@@ -21943,6 +22159,9 @@
       </c>
       <c r="M435" s="1">
         <v>46085</v>
+      </c>
+      <c r="N435" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.25">
@@ -21959,19 +22178,19 @@
         <v>57</v>
       </c>
       <c r="E436" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F436" t="s">
         <v>23</v>
       </c>
       <c r="G436" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H436" t="s">
+        <v>814</v>
+      </c>
+      <c r="I436" t="s">
         <v>815</v>
-      </c>
-      <c r="I436" t="s">
-        <v>816</v>
       </c>
       <c r="J436" t="s">
         <v>20</v>
@@ -21981,6 +22200,12 @@
       </c>
       <c r="L436" t="s">
         <v>21</v>
+      </c>
+      <c r="M436" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N436" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.25">
@@ -21997,19 +22222,19 @@
         <v>37</v>
       </c>
       <c r="E437" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F437" t="s">
         <v>23</v>
       </c>
       <c r="G437" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H437" t="s">
+        <v>816</v>
+      </c>
+      <c r="I437" t="s">
         <v>817</v>
-      </c>
-      <c r="I437" t="s">
-        <v>818</v>
       </c>
       <c r="J437" t="s">
         <v>20</v>
@@ -22022,6 +22247,9 @@
       </c>
       <c r="M437" s="1">
         <v>46085</v>
+      </c>
+      <c r="N437" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.25">
@@ -22038,19 +22266,19 @@
         <v>52</v>
       </c>
       <c r="E438" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F438" t="s">
         <v>23</v>
       </c>
       <c r="G438" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H438" t="s">
+        <v>818</v>
+      </c>
+      <c r="I438" t="s">
         <v>819</v>
-      </c>
-      <c r="I438" t="s">
-        <v>820</v>
       </c>
       <c r="J438" t="s">
         <v>20</v>
@@ -22060,6 +22288,12 @@
       </c>
       <c r="L438" t="s">
         <v>21</v>
+      </c>
+      <c r="M438" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N438" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.25">
@@ -22076,19 +22310,19 @@
         <v>92</v>
       </c>
       <c r="E439" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F439" t="s">
         <v>23</v>
       </c>
       <c r="G439" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H439" t="s">
+        <v>820</v>
+      </c>
+      <c r="I439" t="s">
         <v>821</v>
-      </c>
-      <c r="I439" t="s">
-        <v>822</v>
       </c>
       <c r="J439" t="s">
         <v>20</v>
@@ -22101,6 +22335,9 @@
       </c>
       <c r="M439" s="1">
         <v>46085</v>
+      </c>
+      <c r="N439" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.25">
@@ -22117,19 +22354,19 @@
         <v>14</v>
       </c>
       <c r="E440" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F440" t="s">
         <v>23</v>
       </c>
       <c r="G440" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H440" t="s">
+        <v>822</v>
+      </c>
+      <c r="I440" t="s">
         <v>823</v>
-      </c>
-      <c r="I440" t="s">
-        <v>824</v>
       </c>
       <c r="J440" t="s">
         <v>20</v>
@@ -22139,6 +22376,12 @@
       </c>
       <c r="L440" t="s">
         <v>21</v>
+      </c>
+      <c r="M440" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N440" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.25">
@@ -22155,19 +22398,19 @@
         <v>83</v>
       </c>
       <c r="E441" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F441" t="s">
         <v>23</v>
       </c>
       <c r="G441" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H441" t="s">
         <v>101</v>
       </c>
       <c r="I441" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J441" t="s">
         <v>20</v>
@@ -22177,6 +22420,12 @@
       </c>
       <c r="L441" t="s">
         <v>21</v>
+      </c>
+      <c r="M441" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N441" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.25">
@@ -22193,7 +22442,7 @@
         <v>95</v>
       </c>
       <c r="E442" t="s">
-        <v>826</v>
+        <v>645</v>
       </c>
       <c r="F442" t="s">
         <v>130</v>
@@ -22202,10 +22451,10 @@
         <v>6</v>
       </c>
       <c r="H442" t="s">
+        <v>826</v>
+      </c>
+      <c r="I442" t="s">
         <v>827</v>
-      </c>
-      <c r="I442" t="s">
-        <v>828</v>
       </c>
       <c r="J442" t="s">
         <v>116</v>
@@ -22234,10 +22483,10 @@
         <v>62</v>
       </c>
       <c r="H443" t="s">
+        <v>828</v>
+      </c>
+      <c r="I443" t="s">
         <v>829</v>
-      </c>
-      <c r="I443" t="s">
-        <v>830</v>
       </c>
       <c r="J443" t="s">
         <v>20</v>
@@ -22257,7 +22506,7 @@
         <v>489</v>
       </c>
       <c r="E444" t="s">
-        <v>826</v>
+        <v>645</v>
       </c>
       <c r="F444" t="s">
         <v>130</v>
@@ -22269,7 +22518,7 @@
         <v>352</v>
       </c>
       <c r="I444" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J444" t="s">
         <v>116</v>
@@ -22289,7 +22538,7 @@
         <v>22</v>
       </c>
       <c r="E445" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F445" t="s">
         <v>23</v>
@@ -22298,10 +22547,10 @@
         <v>6</v>
       </c>
       <c r="H445" t="s">
-        <v>832</v>
+        <v>903</v>
       </c>
       <c r="I445" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J445" t="s">
         <v>26</v>
@@ -22311,6 +22560,9 @@
       </c>
       <c r="L445" t="s">
         <v>21</v>
+      </c>
+      <c r="M445" s="1">
+        <v>46087</v>
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.25">
@@ -22327,19 +22579,19 @@
         <v>52</v>
       </c>
       <c r="E446" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F446" t="s">
         <v>23</v>
       </c>
       <c r="G446" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H446" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="I446" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J446" t="s">
         <v>26</v>
@@ -22349,6 +22601,12 @@
       </c>
       <c r="L446" t="s">
         <v>21</v>
+      </c>
+      <c r="M446" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N446" s="1">
+        <v>46090</v>
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.25">
@@ -22374,10 +22632,10 @@
         <v>17</v>
       </c>
       <c r="H447" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="I447" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J447" t="s">
         <v>26</v>
@@ -22418,10 +22676,10 @@
         <v>6</v>
       </c>
       <c r="H448" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="I448" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J448" t="s">
         <v>20</v>
@@ -22433,7 +22691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>46083</v>
       </c>
@@ -22447,19 +22705,19 @@
         <v>489</v>
       </c>
       <c r="E449" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F449" t="s">
         <v>23</v>
       </c>
       <c r="G449" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H449" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="I449" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J449" t="s">
         <v>20</v>
@@ -22470,8 +22728,14 @@
       <c r="L449" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M449" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N449" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>46083</v>
       </c>
@@ -22485,19 +22749,19 @@
         <v>49</v>
       </c>
       <c r="E450" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F450" t="s">
         <v>23</v>
       </c>
       <c r="G450" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H450" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="I450" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="J450" t="s">
         <v>26</v>
@@ -22511,8 +22775,11 @@
       <c r="M450" s="1">
         <v>46085</v>
       </c>
-    </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N450" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>46083</v>
       </c>
@@ -22526,19 +22793,19 @@
         <v>37</v>
       </c>
       <c r="E451" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F451" t="s">
         <v>23</v>
       </c>
       <c r="G451" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H451" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="I451" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="J451" t="s">
         <v>26</v>
@@ -22552,8 +22819,11 @@
       <c r="M451" s="1">
         <v>46085</v>
       </c>
-    </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N451" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>46083</v>
       </c>
@@ -22567,19 +22837,19 @@
         <v>37</v>
       </c>
       <c r="E452" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F452" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G452" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H452" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="I452" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="J452" t="s">
         <v>20</v>
@@ -22590,8 +22860,14 @@
       <c r="L452" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M452" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N452" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>46083</v>
       </c>
@@ -22605,19 +22881,19 @@
         <v>37</v>
       </c>
       <c r="E453" t="s">
-        <v>731</v>
+        <v>15</v>
       </c>
       <c r="F453" t="s">
         <v>23</v>
       </c>
       <c r="G453" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H453" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="I453" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J453" t="s">
         <v>26</v>
@@ -22631,8 +22907,11 @@
       <c r="M453" s="1">
         <v>46085</v>
       </c>
-    </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N453" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>46083</v>
       </c>
@@ -22646,31 +22925,29 @@
         <v>40</v>
       </c>
       <c r="E454" t="s">
-        <v>724</v>
+        <v>60</v>
       </c>
       <c r="F454" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G454" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="H454" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="I454" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="J454" t="s">
         <v>20</v>
       </c>
-      <c r="K454" s="1">
-        <v>46091</v>
-      </c>
+      <c r="K454" s="1"/>
       <c r="L454" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>46083</v>
       </c>
@@ -22684,7 +22961,7 @@
         <v>214</v>
       </c>
       <c r="E455" t="s">
-        <v>826</v>
+        <v>645</v>
       </c>
       <c r="F455" t="s">
         <v>130</v>
@@ -22696,13 +22973,13 @@
         <v>251</v>
       </c>
       <c r="I455" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="J455" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>46083</v>
       </c>
@@ -22716,7 +22993,7 @@
         <v>43</v>
       </c>
       <c r="E456" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F456" t="s">
         <v>23</v>
@@ -22725,10 +23002,10 @@
         <v>6</v>
       </c>
       <c r="H456" t="s">
-        <v>375</v>
+        <v>904</v>
       </c>
       <c r="I456" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="J456" t="s">
         <v>20</v>
@@ -22739,8 +23016,11 @@
       <c r="L456" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M456" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>46083</v>
       </c>
@@ -22754,7 +23034,7 @@
         <v>14</v>
       </c>
       <c r="E457" t="s">
-        <v>724</v>
+        <v>885</v>
       </c>
       <c r="F457" t="s">
         <v>23</v>
@@ -22763,10 +23043,10 @@
         <v>6</v>
       </c>
       <c r="H457" t="s">
-        <v>649</v>
+        <v>905</v>
       </c>
       <c r="I457" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="J457" t="s">
         <v>20</v>
@@ -22778,7 +23058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <v>46084</v>
       </c>
@@ -22792,7 +23072,7 @@
         <v>293</v>
       </c>
       <c r="E458" t="s">
-        <v>826</v>
+        <v>724</v>
       </c>
       <c r="F458" t="s">
         <v>130</v>
@@ -22801,16 +23081,22 @@
         <v>6</v>
       </c>
       <c r="H458" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="I458" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J458" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K458" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L458" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>46084</v>
       </c>
@@ -22824,19 +23110,19 @@
         <v>27</v>
       </c>
       <c r="E459" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F459" t="s">
         <v>23</v>
       </c>
       <c r="G459" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H459" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="I459" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="J459" t="s">
         <v>26</v>
@@ -22847,8 +23133,14 @@
       <c r="L459" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M459" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N459" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>46084</v>
       </c>
@@ -22862,19 +23154,19 @@
         <v>95</v>
       </c>
       <c r="E460" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F460" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G460" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H460" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="I460" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="J460" t="s">
         <v>26</v>
@@ -22885,8 +23177,14 @@
       <c r="L460" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M460" s="1">
+        <v>46091</v>
+      </c>
+      <c r="N460" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>46084</v>
       </c>
@@ -22900,19 +23198,19 @@
         <v>52</v>
       </c>
       <c r="E461" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F461" t="s">
         <v>23</v>
       </c>
       <c r="G461" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H461" t="s">
         <v>454</v>
       </c>
       <c r="I461" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="J461" t="s">
         <v>26</v>
@@ -22923,8 +23221,14 @@
       <c r="L461" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M461" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N461" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>46084</v>
       </c>
@@ -22938,7 +23242,7 @@
         <v>14</v>
       </c>
       <c r="E462" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F462" t="s">
         <v>23</v>
@@ -22947,10 +23251,10 @@
         <v>6</v>
       </c>
       <c r="H462" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="I462" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="J462" t="s">
         <v>20</v>
@@ -22961,8 +23265,11 @@
       <c r="L462" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M462" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>46084</v>
       </c>
@@ -22976,7 +23283,7 @@
         <v>52</v>
       </c>
       <c r="E463" t="s">
-        <v>724</v>
+        <v>885</v>
       </c>
       <c r="F463" t="s">
         <v>23</v>
@@ -22985,10 +23292,10 @@
         <v>6</v>
       </c>
       <c r="H463" t="s">
-        <v>464</v>
+        <v>906</v>
       </c>
       <c r="I463" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="J463" t="s">
         <v>26</v>
@@ -22999,8 +23306,11 @@
       <c r="L463" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M463" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>46084</v>
       </c>
@@ -23014,19 +23324,19 @@
         <v>43</v>
       </c>
       <c r="E464" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F464" t="s">
         <v>23</v>
       </c>
       <c r="G464" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H464" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="I464" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="J464" t="s">
         <v>26</v>
@@ -23037,8 +23347,14 @@
       <c r="L464" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M464" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N464" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>46085</v>
       </c>
@@ -23052,7 +23368,7 @@
         <v>92</v>
       </c>
       <c r="E465" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F465" t="s">
         <v>23</v>
@@ -23064,7 +23380,7 @@
         <v>305</v>
       </c>
       <c r="I465" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="J465" t="s">
         <v>20</v>
@@ -23076,7 +23392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>46085</v>
       </c>
@@ -23099,10 +23415,10 @@
         <v>6</v>
       </c>
       <c r="H466" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="I466" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="J466" t="s">
         <v>20</v>
@@ -23114,7 +23430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>46085</v>
       </c>
@@ -23128,7 +23444,7 @@
         <v>49</v>
       </c>
       <c r="E467" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="F467" t="s">
         <v>23</v>
@@ -23137,10 +23453,10 @@
         <v>6</v>
       </c>
       <c r="H467" t="s">
-        <v>870</v>
+        <v>907</v>
       </c>
       <c r="I467" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="J467" t="s">
         <v>20</v>
@@ -23152,7 +23468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>46085</v>
       </c>
@@ -23166,19 +23482,19 @@
         <v>22</v>
       </c>
       <c r="E468" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F468" t="s">
         <v>23</v>
       </c>
       <c r="G468" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H468" t="s">
         <v>382</v>
       </c>
       <c r="I468" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="J468" t="s">
         <v>20</v>
@@ -23189,8 +23505,14 @@
       <c r="L468" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M468" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N468" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <v>46085</v>
       </c>
@@ -23204,7 +23526,7 @@
         <v>57</v>
       </c>
       <c r="E469" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="F469" t="s">
         <v>23</v>
@@ -23213,10 +23535,10 @@
         <v>6</v>
       </c>
       <c r="H469" t="s">
-        <v>873</v>
+        <v>908</v>
       </c>
       <c r="I469" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="J469" t="s">
         <v>26</v>
@@ -23228,7 +23550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>46085</v>
       </c>
@@ -23242,7 +23564,7 @@
         <v>52</v>
       </c>
       <c r="E470" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F470" t="s">
         <v>23</v>
@@ -23254,7 +23576,7 @@
         <v>763</v>
       </c>
       <c r="I470" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="J470" t="s">
         <v>20</v>
@@ -23265,8 +23587,11 @@
       <c r="L470" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M470" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>46085</v>
       </c>
@@ -23280,7 +23605,7 @@
         <v>52</v>
       </c>
       <c r="E471" t="s">
-        <v>724</v>
+        <v>909</v>
       </c>
       <c r="F471" t="s">
         <v>23</v>
@@ -23289,10 +23614,10 @@
         <v>6</v>
       </c>
       <c r="H471" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="I471" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="J471" t="s">
         <v>26</v>
@@ -23303,8 +23628,14 @@
       <c r="L471" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M471" s="1">
+        <v>46091</v>
+      </c>
+      <c r="N471" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>46085</v>
       </c>
@@ -23318,7 +23649,7 @@
         <v>57</v>
       </c>
       <c r="E472" t="s">
-        <v>724</v>
+        <v>909</v>
       </c>
       <c r="F472" t="s">
         <v>23</v>
@@ -23330,7 +23661,7 @@
         <v>496</v>
       </c>
       <c r="I472" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="J472" t="s">
         <v>26</v>
@@ -23341,8 +23672,14 @@
       <c r="L472" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M472" s="1">
+        <v>46091</v>
+      </c>
+      <c r="N472" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>46085</v>
       </c>
@@ -23365,10 +23702,10 @@
         <v>6</v>
       </c>
       <c r="H473" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="I473" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="J473" t="s">
         <v>20</v>
@@ -23380,7 +23717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>46085</v>
       </c>
@@ -23394,13 +23731,13 @@
         <v>83</v>
       </c>
       <c r="E474" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F474" t="s">
         <v>23</v>
       </c>
       <c r="G474" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H474" t="s">
         <v>483</v>
@@ -23417,8 +23754,14 @@
       <c r="L474" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M474" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N474" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>46086</v>
       </c>
@@ -23441,10 +23784,10 @@
         <v>6</v>
       </c>
       <c r="H475" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="I475" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="J475" t="s">
         <v>20</v>
@@ -23456,7 +23799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>46086</v>
       </c>
@@ -23470,19 +23813,19 @@
         <v>105</v>
       </c>
       <c r="E476" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F476" t="s">
         <v>86</v>
       </c>
       <c r="G476" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H476" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="I476" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="J476" t="s">
         <v>21</v>
@@ -23493,8 +23836,14 @@
       <c r="L476" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M476" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N476" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>46086</v>
       </c>
@@ -23508,7 +23857,7 @@
         <v>46</v>
       </c>
       <c r="E477" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F477" t="s">
         <v>86</v>
@@ -23517,10 +23866,10 @@
         <v>6</v>
       </c>
       <c r="H477" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="I477" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="J477" t="s">
         <v>21</v>
@@ -23531,8 +23880,11 @@
       <c r="L477" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M477" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <v>46086</v>
       </c>
@@ -23546,7 +23898,7 @@
         <v>65</v>
       </c>
       <c r="E478" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="F478" t="s">
         <v>86</v>
@@ -23569,8 +23921,11 @@
       <c r="L478" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M478" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>46086</v>
       </c>
@@ -23593,10 +23948,10 @@
         <v>6</v>
       </c>
       <c r="H479" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="I479" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="J479" t="s">
         <v>20</v>
@@ -23608,7 +23963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>46086</v>
       </c>
@@ -23631,10 +23986,10 @@
         <v>6</v>
       </c>
       <c r="H480" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="I480" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="J480" t="s">
         <v>20</v>
@@ -23646,7 +24001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>46086</v>
       </c>
@@ -23660,7 +24015,7 @@
         <v>65</v>
       </c>
       <c r="E481" t="s">
-        <v>889</v>
+        <v>731</v>
       </c>
       <c r="F481" t="s">
         <v>23</v>
@@ -23669,13 +24024,13 @@
         <v>6</v>
       </c>
       <c r="H481" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I481" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="J481" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="K481" s="1">
         <v>46090</v>
@@ -23683,8 +24038,11 @@
       <c r="L481" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M481" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>46086</v>
       </c>
@@ -23707,10 +24065,10 @@
         <v>6</v>
       </c>
       <c r="H482" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="I482" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="J482" t="s">
         <v>20</v>
@@ -23722,7 +24080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>46086</v>
       </c>
@@ -23745,10 +24103,10 @@
         <v>6</v>
       </c>
       <c r="H483" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I483" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="J483" t="s">
         <v>26</v>
@@ -23760,7 +24118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>46086</v>
       </c>
@@ -23786,10 +24144,10 @@
         <v>447</v>
       </c>
       <c r="I484" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="J484" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K484" s="1">
         <v>46091</v>
@@ -23798,7 +24156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>46086</v>
       </c>
@@ -23812,7 +24170,7 @@
         <v>214</v>
       </c>
       <c r="E485" t="s">
-        <v>826</v>
+        <v>724</v>
       </c>
       <c r="F485" t="s">
         <v>130</v>
@@ -23821,16 +24179,22 @@
         <v>6</v>
       </c>
       <c r="H485" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="I485" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="J485" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K485" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L485" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>46086</v>
       </c>
@@ -23844,16 +24208,16 @@
         <v>49</v>
       </c>
       <c r="E486" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F486" t="s">
         <v>23</v>
       </c>
       <c r="G486" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H486" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="I486" t="s">
         <v>728</v>
@@ -23867,8 +24231,14 @@
       <c r="L486" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M486" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N486" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>46086</v>
       </c>
@@ -23882,19 +24252,19 @@
         <v>52</v>
       </c>
       <c r="E487" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F487" t="s">
         <v>23</v>
       </c>
       <c r="G487" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H487" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="I487" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="J487" t="s">
         <v>26</v>
@@ -23905,8 +24275,14 @@
       <c r="L487" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M487" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N487" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>46086</v>
       </c>
@@ -23920,7 +24296,7 @@
         <v>52</v>
       </c>
       <c r="E488" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="F488" t="s">
         <v>23</v>
@@ -23929,10 +24305,10 @@
         <v>6</v>
       </c>
       <c r="H488" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="I488" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="J488" t="s">
         <v>26</v>
@@ -23944,7 +24320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>46086</v>
       </c>
@@ -23958,19 +24334,19 @@
         <v>83</v>
       </c>
       <c r="E489" t="s">
-        <v>724</v>
+        <v>15</v>
       </c>
       <c r="F489" t="s">
         <v>23</v>
       </c>
       <c r="G489" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H489" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="I489" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J489" t="s">
         <v>26</v>
@@ -23980,6 +24356,981 @@
       </c>
       <c r="L489" t="s">
         <v>21</v>
+      </c>
+      <c r="M489" s="1">
+        <v>46087</v>
+      </c>
+      <c r="N489" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A490" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B490">
+        <v>2003932022</v>
+      </c>
+      <c r="C490">
+        <v>520279</v>
+      </c>
+      <c r="D490" t="s">
+        <v>14</v>
+      </c>
+      <c r="E490" t="s">
+        <v>909</v>
+      </c>
+      <c r="F490" t="s">
+        <v>16</v>
+      </c>
+      <c r="G490" t="s">
+        <v>6</v>
+      </c>
+      <c r="H490" t="s">
+        <v>911</v>
+      </c>
+      <c r="I490" t="s">
+        <v>759</v>
+      </c>
+      <c r="J490" t="s">
+        <v>21</v>
+      </c>
+      <c r="K490" s="1">
+        <v>46090</v>
+      </c>
+      <c r="L490" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A491" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B491">
+        <v>2003944898</v>
+      </c>
+      <c r="C491">
+        <v>520145</v>
+      </c>
+      <c r="D491" t="s">
+        <v>65</v>
+      </c>
+      <c r="E491" t="s">
+        <v>724</v>
+      </c>
+      <c r="F491" t="s">
+        <v>23</v>
+      </c>
+      <c r="G491" t="s">
+        <v>6</v>
+      </c>
+      <c r="H491" t="s">
+        <v>912</v>
+      </c>
+      <c r="I491" t="s">
+        <v>913</v>
+      </c>
+      <c r="J491" t="s">
+        <v>20</v>
+      </c>
+      <c r="K491" s="1">
+        <v>46091</v>
+      </c>
+      <c r="L491" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A492" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B492">
+        <v>2003934865</v>
+      </c>
+      <c r="C492">
+        <v>519862</v>
+      </c>
+      <c r="D492" t="s">
+        <v>98</v>
+      </c>
+      <c r="E492" t="s">
+        <v>645</v>
+      </c>
+      <c r="F492" t="s">
+        <v>23</v>
+      </c>
+      <c r="G492" t="s">
+        <v>6</v>
+      </c>
+      <c r="H492" t="s">
+        <v>914</v>
+      </c>
+      <c r="I492" t="s">
+        <v>915</v>
+      </c>
+      <c r="J492" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A493" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B493">
+        <v>2003929582</v>
+      </c>
+      <c r="C493">
+        <v>519947</v>
+      </c>
+      <c r="D493" t="s">
+        <v>14</v>
+      </c>
+      <c r="E493" t="s">
+        <v>731</v>
+      </c>
+      <c r="F493" t="s">
+        <v>23</v>
+      </c>
+      <c r="G493" t="s">
+        <v>6</v>
+      </c>
+      <c r="H493" t="s">
+        <v>708</v>
+      </c>
+      <c r="I493" t="s">
+        <v>916</v>
+      </c>
+      <c r="J493" t="s">
+        <v>20</v>
+      </c>
+      <c r="K493" s="1">
+        <v>46090</v>
+      </c>
+      <c r="L493" t="s">
+        <v>21</v>
+      </c>
+      <c r="M493" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A494" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B494">
+        <v>2003917124</v>
+      </c>
+      <c r="C494">
+        <v>519446</v>
+      </c>
+      <c r="D494" t="s">
+        <v>331</v>
+      </c>
+      <c r="E494" t="s">
+        <v>724</v>
+      </c>
+      <c r="F494" t="s">
+        <v>130</v>
+      </c>
+      <c r="G494" t="s">
+        <v>6</v>
+      </c>
+      <c r="H494" t="s">
+        <v>917</v>
+      </c>
+      <c r="I494" t="s">
+        <v>918</v>
+      </c>
+      <c r="J494" t="s">
+        <v>20</v>
+      </c>
+      <c r="K494" s="1">
+        <v>46097</v>
+      </c>
+      <c r="L494" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A495" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B495">
+        <v>2003943385</v>
+      </c>
+      <c r="C495">
+        <v>519076</v>
+      </c>
+      <c r="D495" t="s">
+        <v>49</v>
+      </c>
+      <c r="E495" t="s">
+        <v>724</v>
+      </c>
+      <c r="F495" t="s">
+        <v>23</v>
+      </c>
+      <c r="G495" t="s">
+        <v>6</v>
+      </c>
+      <c r="H495" t="s">
+        <v>919</v>
+      </c>
+      <c r="I495" t="s">
+        <v>920</v>
+      </c>
+      <c r="J495" t="s">
+        <v>20</v>
+      </c>
+      <c r="K495" s="1">
+        <v>46091</v>
+      </c>
+      <c r="L495" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A496" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B496">
+        <v>2003869876</v>
+      </c>
+      <c r="C496">
+        <v>6685547</v>
+      </c>
+      <c r="D496" t="s">
+        <v>214</v>
+      </c>
+      <c r="E496" t="s">
+        <v>645</v>
+      </c>
+      <c r="F496" t="s">
+        <v>130</v>
+      </c>
+      <c r="G496" t="s">
+        <v>6</v>
+      </c>
+      <c r="H496" t="s">
+        <v>921</v>
+      </c>
+      <c r="I496" t="s">
+        <v>922</v>
+      </c>
+      <c r="J496" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A497" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B497">
+        <v>2003940145</v>
+      </c>
+      <c r="C497">
+        <v>6686034</v>
+      </c>
+      <c r="D497" t="s">
+        <v>52</v>
+      </c>
+      <c r="E497" t="s">
+        <v>724</v>
+      </c>
+      <c r="F497" t="s">
+        <v>23</v>
+      </c>
+      <c r="G497" t="s">
+        <v>6</v>
+      </c>
+      <c r="H497" t="s">
+        <v>50</v>
+      </c>
+      <c r="I497" t="s">
+        <v>923</v>
+      </c>
+      <c r="J497" t="s">
+        <v>26</v>
+      </c>
+      <c r="K497" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L497" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B498">
+        <v>2003944260</v>
+      </c>
+      <c r="C498">
+        <v>6686094</v>
+      </c>
+      <c r="D498" t="s">
+        <v>37</v>
+      </c>
+      <c r="E498" t="s">
+        <v>724</v>
+      </c>
+      <c r="F498" t="s">
+        <v>23</v>
+      </c>
+      <c r="G498" t="s">
+        <v>6</v>
+      </c>
+      <c r="H498" t="s">
+        <v>924</v>
+      </c>
+      <c r="I498" t="s">
+        <v>925</v>
+      </c>
+      <c r="J498" t="s">
+        <v>20</v>
+      </c>
+      <c r="K498" s="1">
+        <v>46091</v>
+      </c>
+      <c r="L498" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B499">
+        <v>2003889741</v>
+      </c>
+      <c r="C499">
+        <v>522363</v>
+      </c>
+      <c r="D499" t="s">
+        <v>49</v>
+      </c>
+      <c r="E499" t="s">
+        <v>724</v>
+      </c>
+      <c r="F499" t="s">
+        <v>23</v>
+      </c>
+      <c r="G499" t="s">
+        <v>6</v>
+      </c>
+      <c r="H499" t="s">
+        <v>926</v>
+      </c>
+      <c r="I499" t="s">
+        <v>927</v>
+      </c>
+      <c r="J499" t="s">
+        <v>20</v>
+      </c>
+      <c r="K499" s="1">
+        <v>46091</v>
+      </c>
+      <c r="L499" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B500">
+        <v>2003946360</v>
+      </c>
+      <c r="C500">
+        <v>522339</v>
+      </c>
+      <c r="D500" t="s">
+        <v>52</v>
+      </c>
+      <c r="E500" t="s">
+        <v>724</v>
+      </c>
+      <c r="F500" t="s">
+        <v>23</v>
+      </c>
+      <c r="G500" t="s">
+        <v>6</v>
+      </c>
+      <c r="H500" t="s">
+        <v>928</v>
+      </c>
+      <c r="I500" t="s">
+        <v>929</v>
+      </c>
+      <c r="J500" t="s">
+        <v>20</v>
+      </c>
+      <c r="K500" s="1">
+        <v>46094</v>
+      </c>
+      <c r="L500" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B501">
+        <v>2003926617</v>
+      </c>
+      <c r="C501">
+        <v>522226</v>
+      </c>
+      <c r="D501" t="s">
+        <v>331</v>
+      </c>
+      <c r="E501" t="s">
+        <v>825</v>
+      </c>
+      <c r="F501" t="s">
+        <v>130</v>
+      </c>
+      <c r="G501" t="s">
+        <v>6</v>
+      </c>
+      <c r="H501" t="s">
+        <v>930</v>
+      </c>
+      <c r="I501" t="s">
+        <v>931</v>
+      </c>
+      <c r="J501" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B502">
+        <v>2003886260</v>
+      </c>
+      <c r="C502">
+        <v>521895</v>
+      </c>
+      <c r="D502" t="s">
+        <v>331</v>
+      </c>
+      <c r="E502" t="s">
+        <v>825</v>
+      </c>
+      <c r="F502" t="s">
+        <v>130</v>
+      </c>
+      <c r="G502" t="s">
+        <v>6</v>
+      </c>
+      <c r="H502" t="s">
+        <v>932</v>
+      </c>
+      <c r="I502" t="s">
+        <v>933</v>
+      </c>
+      <c r="J502" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B503">
+        <v>2003941970</v>
+      </c>
+      <c r="C503">
+        <v>521924</v>
+      </c>
+      <c r="D503" t="s">
+        <v>40</v>
+      </c>
+      <c r="E503" t="s">
+        <v>724</v>
+      </c>
+      <c r="F503" t="s">
+        <v>23</v>
+      </c>
+      <c r="G503" t="s">
+        <v>6</v>
+      </c>
+      <c r="H503" t="s">
+        <v>840</v>
+      </c>
+      <c r="I503" t="s">
+        <v>934</v>
+      </c>
+      <c r="J503" t="s">
+        <v>20</v>
+      </c>
+      <c r="K503" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L503" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B504">
+        <v>2003936744</v>
+      </c>
+      <c r="C504">
+        <v>6686364</v>
+      </c>
+      <c r="D504" t="s">
+        <v>43</v>
+      </c>
+      <c r="E504" t="s">
+        <v>724</v>
+      </c>
+      <c r="F504" t="s">
+        <v>23</v>
+      </c>
+      <c r="G504" t="s">
+        <v>6</v>
+      </c>
+      <c r="H504" t="s">
+        <v>935</v>
+      </c>
+      <c r="I504" t="s">
+        <v>936</v>
+      </c>
+      <c r="J504" t="s">
+        <v>20</v>
+      </c>
+      <c r="K504" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L504" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B505">
+        <v>2003934182</v>
+      </c>
+      <c r="C505">
+        <v>6686635</v>
+      </c>
+      <c r="D505" t="s">
+        <v>331</v>
+      </c>
+      <c r="E505" t="s">
+        <v>825</v>
+      </c>
+      <c r="F505" t="s">
+        <v>130</v>
+      </c>
+      <c r="G505" t="s">
+        <v>6</v>
+      </c>
+      <c r="H505" t="s">
+        <v>937</v>
+      </c>
+      <c r="I505" t="s">
+        <v>938</v>
+      </c>
+      <c r="J505" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B506">
+        <v>2003869234</v>
+      </c>
+      <c r="C506">
+        <v>6686669</v>
+      </c>
+      <c r="D506" t="s">
+        <v>331</v>
+      </c>
+      <c r="E506" t="s">
+        <v>825</v>
+      </c>
+      <c r="F506" t="s">
+        <v>130</v>
+      </c>
+      <c r="G506" t="s">
+        <v>6</v>
+      </c>
+      <c r="H506" t="s">
+        <v>939</v>
+      </c>
+      <c r="I506" t="s">
+        <v>940</v>
+      </c>
+      <c r="J506" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B507">
+        <v>2003928904</v>
+      </c>
+      <c r="C507">
+        <v>6686882</v>
+      </c>
+      <c r="D507" t="s">
+        <v>43</v>
+      </c>
+      <c r="E507" t="s">
+        <v>724</v>
+      </c>
+      <c r="F507" t="s">
+        <v>23</v>
+      </c>
+      <c r="G507" t="s">
+        <v>6</v>
+      </c>
+      <c r="H507" t="s">
+        <v>315</v>
+      </c>
+      <c r="I507" t="s">
+        <v>941</v>
+      </c>
+      <c r="J507" t="s">
+        <v>20</v>
+      </c>
+      <c r="K507" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L507" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B508">
+        <v>2003676404</v>
+      </c>
+      <c r="C508">
+        <v>6686899</v>
+      </c>
+      <c r="D508" t="s">
+        <v>40</v>
+      </c>
+      <c r="E508" t="s">
+        <v>724</v>
+      </c>
+      <c r="F508" t="s">
+        <v>23</v>
+      </c>
+      <c r="G508" t="s">
+        <v>6</v>
+      </c>
+      <c r="H508" t="s">
+        <v>942</v>
+      </c>
+      <c r="I508" t="s">
+        <v>943</v>
+      </c>
+      <c r="J508" t="s">
+        <v>20</v>
+      </c>
+      <c r="K508" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L508" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B509">
+        <v>2003936758</v>
+      </c>
+      <c r="C509">
+        <v>524980</v>
+      </c>
+      <c r="D509" t="s">
+        <v>129</v>
+      </c>
+      <c r="E509" t="s">
+        <v>825</v>
+      </c>
+      <c r="F509" t="s">
+        <v>130</v>
+      </c>
+      <c r="G509" t="s">
+        <v>6</v>
+      </c>
+      <c r="H509" t="s">
+        <v>611</v>
+      </c>
+      <c r="I509" t="s">
+        <v>944</v>
+      </c>
+      <c r="J509" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B510">
+        <v>2003947718</v>
+      </c>
+      <c r="C510">
+        <v>524947</v>
+      </c>
+      <c r="D510" t="s">
+        <v>95</v>
+      </c>
+      <c r="E510" t="s">
+        <v>825</v>
+      </c>
+      <c r="F510" t="s">
+        <v>23</v>
+      </c>
+      <c r="G510" t="s">
+        <v>6</v>
+      </c>
+      <c r="H510" t="s">
+        <v>945</v>
+      </c>
+      <c r="I510" t="s">
+        <v>946</v>
+      </c>
+      <c r="J510" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B511">
+        <v>2003844332</v>
+      </c>
+      <c r="C511">
+        <v>524555</v>
+      </c>
+      <c r="D511" t="s">
+        <v>319</v>
+      </c>
+      <c r="E511" t="s">
+        <v>724</v>
+      </c>
+      <c r="F511" t="s">
+        <v>23</v>
+      </c>
+      <c r="G511" t="s">
+        <v>6</v>
+      </c>
+      <c r="H511" t="s">
+        <v>947</v>
+      </c>
+      <c r="I511" t="s">
+        <v>948</v>
+      </c>
+      <c r="J511" t="s">
+        <v>21</v>
+      </c>
+      <c r="K511" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L511" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B512">
+        <v>2003938006</v>
+      </c>
+      <c r="C512">
+        <v>524118</v>
+      </c>
+      <c r="D512" t="s">
+        <v>49</v>
+      </c>
+      <c r="E512" t="s">
+        <v>724</v>
+      </c>
+      <c r="F512" t="s">
+        <v>23</v>
+      </c>
+      <c r="G512" t="s">
+        <v>6</v>
+      </c>
+      <c r="H512" t="s">
+        <v>949</v>
+      </c>
+      <c r="I512" t="s">
+        <v>950</v>
+      </c>
+      <c r="J512" t="s">
+        <v>20</v>
+      </c>
+      <c r="K512" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L512" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B513">
+        <v>2003946270</v>
+      </c>
+      <c r="C513">
+        <v>523610</v>
+      </c>
+      <c r="D513" t="s">
+        <v>46</v>
+      </c>
+      <c r="E513" t="s">
+        <v>724</v>
+      </c>
+      <c r="F513" t="s">
+        <v>23</v>
+      </c>
+      <c r="G513" t="s">
+        <v>6</v>
+      </c>
+      <c r="H513" t="s">
+        <v>951</v>
+      </c>
+      <c r="I513" t="s">
+        <v>952</v>
+      </c>
+      <c r="J513" t="s">
+        <v>21</v>
+      </c>
+      <c r="K513" s="1">
+        <v>46093</v>
+      </c>
+      <c r="L513" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B514">
+        <v>2003587808</v>
+      </c>
+      <c r="C514">
+        <v>6687149</v>
+      </c>
+      <c r="D514" t="s">
+        <v>98</v>
+      </c>
+      <c r="E514" t="s">
+        <v>885</v>
+      </c>
+      <c r="F514" t="s">
+        <v>86</v>
+      </c>
+      <c r="G514" t="s">
+        <v>6</v>
+      </c>
+      <c r="H514" t="s">
+        <v>953</v>
+      </c>
+      <c r="I514" t="s">
+        <v>954</v>
+      </c>
+      <c r="J514" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B515">
+        <v>2003945784</v>
+      </c>
+      <c r="C515">
+        <v>6687509</v>
+      </c>
+      <c r="D515" t="s">
+        <v>52</v>
+      </c>
+      <c r="E515" t="s">
+        <v>724</v>
+      </c>
+      <c r="F515" t="s">
+        <v>23</v>
+      </c>
+      <c r="G515" t="s">
+        <v>6</v>
+      </c>
+      <c r="H515" t="s">
+        <v>955</v>
+      </c>
+      <c r="I515" t="s">
+        <v>956</v>
+      </c>
+      <c r="J515" t="s">
+        <v>20</v>
+      </c>
+      <c r="K515" s="1">
+        <v>46094</v>
+      </c>
+      <c r="L515" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B516">
+        <v>2003921423</v>
+      </c>
+      <c r="C516">
+        <v>268054</v>
+      </c>
+      <c r="D516" t="s">
+        <v>957</v>
+      </c>
+      <c r="E516" t="s">
+        <v>825</v>
+      </c>
+      <c r="F516" t="s">
+        <v>30</v>
+      </c>
+      <c r="G516" t="s">
+        <v>6</v>
+      </c>
+      <c r="H516" t="s">
+        <v>958</v>
+      </c>
+      <c r="I516" t="s">
+        <v>959</v>
+      </c>
+      <c r="J516" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
